--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="116">
   <si>
     <t>Materia</t>
   </si>
@@ -162,15 +162,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
@@ -222,151 +222,151 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
     <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
   </si>
 </sst>
 </file>
@@ -855,7 +855,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -909,7 +909,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -932,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1009,7 +1009,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1086,7 +1086,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1163,7 +1163,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1400,7 +1400,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1477,7 +1477,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1554,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1577,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1631,7 +1631,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1760,7 +1760,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -1814,7 +1814,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -1837,7 +1837,7 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>-1</v>
@@ -1891,7 +1891,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -1914,7 +1914,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>7</v>
@@ -1941,7 +1941,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -1955,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2009,7 +2009,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2032,7 +2032,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2086,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2109,7 +2109,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>-1</v>
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2186,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2263,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2317,7 +2317,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2340,7 +2340,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2394,7 +2394,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2471,7 +2471,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2604,7 +2604,7 @@
         <v>120</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>96</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2722,7 +2722,7 @@
         <v>120</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2781,7 +2781,7 @@
         <v>120</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>120</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>84</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>116</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>120</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>120</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -3217,7 +3217,7 @@
         <v>116</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>120</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         <v>120</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         <v>112</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>88</v>
@@ -3449,7 +3449,7 @@
         <v>116</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>120</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>120</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>120</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>92</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>104</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>120</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3906,13 +3906,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>100</v>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>22</v>
@@ -3964,57 +3964,60 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4025,28 +4028,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>21</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>42.86</v>
+        <v>47.62</v>
       </c>
       <c r="G6">
-        <v>57.14</v>
+        <v>52.38</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4057,28 +4060,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>21</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>47.62</v>
+        <v>66.67</v>
       </c>
       <c r="G7">
-        <v>52.38</v>
+        <v>33.33</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4094,7 +4097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4129,13 +4132,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>47</v>
@@ -4149,24 +4152,24 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -4175,10 +4178,10 @@
         <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4189,13 +4192,13 @@
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>47</v>
@@ -4203,10 +4206,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920071</v>
+        <v>20330051920073</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
         <v>75</v>
@@ -4218,15 +4221,15 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920071</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
         <v>75</v>
@@ -4238,15 +4241,15 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
@@ -4255,7 +4258,7 @@
         <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
@@ -4263,10 +4266,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920073</v>
+        <v>20330051920359</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>76</v>
@@ -4275,38 +4278,38 @@
         <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920359</v>
+        <v>20330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>77</v>
@@ -4315,7 +4318,7 @@
         <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>47</v>
@@ -4323,59 +4326,59 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920359</v>
+        <v>19330051920014</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920359</v>
+        <v>19330051920014</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>47</v>
@@ -4383,99 +4386,99 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920014</v>
+        <v>20330051920077</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920014</v>
+        <v>20330051920080</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920051</v>
+        <v>20330051920080</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>47</v>
@@ -4483,59 +4486,59 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920051</v>
+        <v>20330051920081</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920051</v>
+        <v>20330051920081</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920077</v>
+        <v>20330051920082</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
         <v>47</v>
@@ -4543,59 +4546,59 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920077</v>
+        <v>20330051920082</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>47</v>
@@ -4603,59 +4606,59 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920080</v>
+        <v>19330051920067</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920080</v>
+        <v>19330051920067</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920081</v>
+        <v>20330051920091</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
         <v>47</v>
@@ -4663,59 +4666,59 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920081</v>
+        <v>20330051920091</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920081</v>
+        <v>20330051920093</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>47</v>
@@ -4723,59 +4726,59 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920087</v>
+        <v>20330051920063</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>47</v>
@@ -4783,99 +4786,99 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920087</v>
+        <v>20330051920063</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920087</v>
+        <v>20330051920064</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920067</v>
+        <v>20330051920064</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920067</v>
+        <v>20330051920065</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920091</v>
+        <v>20330051920065</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>47</v>
@@ -4883,59 +4886,59 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920093</v>
+        <v>20330051920068</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
         <v>47</v>
@@ -4943,482 +4946,62 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920093</v>
+        <v>20330051920068</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920093</v>
+        <v>20330051920070</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>18330051920077</v>
+        <v>20330051920070</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920061</v>
-      </c>
-      <c r="B46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920061</v>
-      </c>
-      <c r="B47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920061</v>
-      </c>
-      <c r="B48" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920063</v>
-      </c>
-      <c r="B49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920063</v>
-      </c>
-      <c r="B50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" t="s">
-        <v>110</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920063</v>
-      </c>
-      <c r="B51" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" t="s">
-        <v>90</v>
-      </c>
-      <c r="D51" t="s">
-        <v>110</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920064</v>
-      </c>
-      <c r="B52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" t="s">
-        <v>91</v>
-      </c>
-      <c r="D52" t="s">
-        <v>111</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920064</v>
-      </c>
-      <c r="B53" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" t="s">
-        <v>91</v>
-      </c>
-      <c r="D53" t="s">
-        <v>111</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920064</v>
-      </c>
-      <c r="B54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" t="s">
-        <v>111</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920065</v>
-      </c>
-      <c r="B55" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" t="s">
-        <v>112</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920065</v>
-      </c>
-      <c r="B56" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920065</v>
-      </c>
-      <c r="B57" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" t="s">
-        <v>112</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920066</v>
-      </c>
-      <c r="B58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C58" t="s">
-        <v>93</v>
-      </c>
-      <c r="D58" t="s">
-        <v>113</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920066</v>
-      </c>
-      <c r="B59" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" t="s">
-        <v>113</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920066</v>
-      </c>
-      <c r="B60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C60" t="s">
-        <v>93</v>
-      </c>
-      <c r="D60" t="s">
-        <v>113</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920068</v>
-      </c>
-      <c r="B61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" t="s">
-        <v>62</v>
-      </c>
-      <c r="D61" t="s">
-        <v>114</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920068</v>
-      </c>
-      <c r="B62" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" t="s">
-        <v>62</v>
-      </c>
-      <c r="D62" t="s">
-        <v>114</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920068</v>
-      </c>
-      <c r="B63" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" t="s">
-        <v>62</v>
-      </c>
-      <c r="D63" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920070</v>
-      </c>
-      <c r="B64" t="s">
-        <v>73</v>
-      </c>
-      <c r="C64" t="s">
-        <v>64</v>
-      </c>
-      <c r="D64" t="s">
-        <v>115</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920070</v>
-      </c>
-      <c r="B65" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" t="s">
-        <v>64</v>
-      </c>
-      <c r="D65" t="s">
-        <v>115</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920070</v>
-      </c>
-      <c r="B66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" t="s">
-        <v>64</v>
-      </c>
-      <c r="D66" t="s">
-        <v>115</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -5460,13 +5043,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5477,13 +5060,13 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5494,13 +5077,13 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5511,13 +5094,13 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5528,282 +5111,282 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920051</v>
+        <v>19330051920014</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920077</v>
+        <v>19330051920051</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920080</v>
+        <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920081</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920082</v>
+        <v>20330051920081</v>
       </c>
       <c r="B11" t="s">
         <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920091</v>
+        <v>20330051920087</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920093</v>
+        <v>19330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920061</v>
+        <v>20330051920091</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920063</v>
+        <v>20330051920093</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920064</v>
+        <v>20330051920061</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920065</v>
+        <v>20330051920063</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920066</v>
+        <v>20330051920064</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920068</v>
+        <v>20330051920065</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920070</v>
+        <v>20330051920066</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920014</v>
+        <v>20330051920068</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -5811,16 +5394,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920067</v>
+        <v>20330051920070</v>
       </c>
       <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
         <v>64</v>
       </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -5831,16 +5414,16 @@
         <v>18330051920077</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
         <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5850,7 +5433,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5882,22 +5465,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920014</v>
+        <v>20330051920041</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5905,22 +5488,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920014</v>
+        <v>20330051920041</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5928,22 +5511,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920067</v>
+        <v>20330051920359</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5951,22 +5534,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920067</v>
+        <v>20330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5974,48 +5557,301 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920077</v>
+        <v>19330051920014</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>19330051920014</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920081</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920081</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920067</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920067</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920093</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920093</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920064</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920064</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920070</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920070</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>18330051920077</v>
       </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="D7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
+      <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="116">
   <si>
     <t>Materia</t>
   </si>
@@ -162,18 +162,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Desc Desc Desc</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -222,6 +222,9 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -342,6 +345,9 @@
     <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
+    <t>CARLOS FERNANDO</t>
+  </si>
+  <si>
     <t>ALAN URIEL</t>
   </si>
   <si>
@@ -361,12 +367,6 @@
   </si>
   <si>
     <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
   </si>
 </sst>
 </file>
@@ -858,10 +858,10 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -912,10 +912,10 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -935,10 +935,10 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -989,10 +989,10 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1012,10 +1012,10 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1066,10 +1066,10 @@
         <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1089,10 +1089,10 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1143,10 +1143,10 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1166,10 +1166,10 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -1220,10 +1220,10 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1237,10 +1237,10 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1255,10 +1255,10 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1272,10 +1272,10 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1326,10 +1326,10 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1349,10 +1349,10 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -1403,10 +1403,10 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1426,10 +1426,10 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -1480,10 +1480,10 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1503,10 +1503,10 @@
         <v>8</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -1557,10 +1557,10 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1580,10 +1580,10 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -1634,10 +1634,10 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1657,10 +1657,10 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -1711,10 +1711,10 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1728,10 +1728,10 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1746,10 +1746,10 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1763,10 +1763,10 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1817,10 +1817,10 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -1840,10 +1840,10 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -1894,10 +1894,10 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -1958,10 +1958,10 @@
         <v>8</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -2012,10 +2012,10 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2035,10 +2035,10 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2089,10 +2089,10 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2112,10 +2112,10 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -2166,10 +2166,10 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2189,10 +2189,10 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>4</v>
@@ -2243,10 +2243,10 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2266,10 +2266,10 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -2320,10 +2320,10 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2343,10 +2343,10 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>6</v>
@@ -2397,10 +2397,10 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2420,10 +2420,10 @@
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>7</v>
@@ -2474,10 +2474,10 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2607,10 +2607,10 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F4">
         <v>92</v>
@@ -2666,10 +2666,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>84</v>
@@ -2725,10 +2725,10 @@
         <v>72</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="F6">
         <v>80</v>
@@ -2784,10 +2784,10 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>102.5</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -2843,10 +2843,10 @@
         <v>72</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -2896,10 +2896,10 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2925,10 +2925,10 @@
         <v>72</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F10">
         <v>80</v>
@@ -2984,10 +2984,10 @@
         <v>72</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F11">
         <v>60</v>
@@ -3043,10 +3043,10 @@
         <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F12">
         <v>76</v>
@@ -3102,10 +3102,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3161,10 +3161,10 @@
         <v>72</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F14">
         <v>72</v>
@@ -3220,10 +3220,10 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F15">
         <v>96</v>
@@ -3273,10 +3273,10 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F17">
         <v>72</v>
@@ -3361,10 +3361,10 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="F18">
         <v>92</v>
@@ -3452,10 +3452,10 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F20">
         <v>92</v>
@@ -3511,10 +3511,10 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>88</v>
@@ -3570,10 +3570,10 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F22">
         <v>76</v>
@@ -3629,10 +3629,10 @@
         <v>72</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F23">
         <v>88</v>
@@ -3688,10 +3688,10 @@
         <v>68</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="F24">
         <v>60</v>
@@ -3747,10 +3747,10 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="F25">
         <v>96</v>
@@ -3806,10 +3806,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -3906,86 +3906,92 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>42.86</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H3">
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>47.62</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>52.38</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3996,28 +4002,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>21</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>42.86</v>
+        <v>66.67</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>33.33</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4028,28 +4034,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>47.62</v>
+        <v>77.27</v>
       </c>
       <c r="G6">
-        <v>52.38</v>
+        <v>22.73</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4060,28 +4066,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>66.67</v>
+        <v>77.27</v>
       </c>
       <c r="G7">
-        <v>33.33</v>
+        <v>22.73</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4097,7 +4103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4122,886 +4128,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920041</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920041</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920071</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920071</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920073</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920073</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920359</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920359</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920074</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920074</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920014</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920014</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920051</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920051</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920077</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920077</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920080</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920080</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920081</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920081</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920082</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920082</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920087</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920087</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920067</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920067</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920091</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920091</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920093</v>
-      </c>
-      <c r="B30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920093</v>
-      </c>
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920061</v>
-      </c>
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920061</v>
-      </c>
-      <c r="B33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920063</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920063</v>
-      </c>
-      <c r="B35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" t="s">
-        <v>89</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920064</v>
-      </c>
-      <c r="B36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920064</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920065</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920065</v>
-      </c>
-      <c r="B39" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920066</v>
-      </c>
-      <c r="B40" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920066</v>
-      </c>
-      <c r="B41" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920068</v>
-      </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" t="s">
-        <v>62</v>
-      </c>
-      <c r="D42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920068</v>
-      </c>
-      <c r="B43" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" t="s">
-        <v>112</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920070</v>
-      </c>
-      <c r="B44" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920070</v>
-      </c>
-      <c r="B45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" t="s">
-        <v>64</v>
-      </c>
-      <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5043,13 +4169,13 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5060,13 +4186,13 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5077,13 +4203,13 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5094,13 +4220,13 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5111,13 +4237,13 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5128,13 +4254,13 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5145,13 +4271,13 @@
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5162,13 +4288,13 @@
         <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5179,13 +4305,13 @@
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5196,13 +4322,13 @@
         <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5213,13 +4339,13 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5230,13 +4356,13 @@
         <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5247,13 +4373,13 @@
         <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5264,13 +4390,13 @@
         <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5281,35 +4407,35 @@
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920061</v>
+        <v>18330051920077</v>
       </c>
       <c r="B17" t="s">
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920063</v>
+        <v>20330051920061</v>
       </c>
       <c r="B18" t="s">
         <v>68</v>
@@ -5318,15 +4444,15 @@
         <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920064</v>
+        <v>20330051920063</v>
       </c>
       <c r="B19" t="s">
         <v>69</v>
@@ -5335,15 +4461,15 @@
         <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920065</v>
+        <v>20330051920064</v>
       </c>
       <c r="B20" t="s">
         <v>70</v>
@@ -5352,15 +4478,15 @@
         <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B21" t="s">
         <v>71</v>
@@ -5369,55 +4495,55 @@
         <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920068</v>
+        <v>20330051920066</v>
       </c>
       <c r="B22" t="s">
         <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920070</v>
+        <v>20330051920068</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>18330051920077</v>
+        <v>20330051920070</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>115</v>
@@ -5433,7 +4559,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5465,392 +4591,116 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920041</v>
+        <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920041</v>
+        <v>18330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920359</v>
+        <v>20330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920359</v>
+        <v>20330051920063</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>47</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920014</v>
+        <v>20330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920014</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920081</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920081</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920067</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920067</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920093</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920093</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920064</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920064</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920070</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920070</v>
-      </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>18330051920077</v>
-      </c>
-      <c r="B18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -165,10 +165,13 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
@@ -4005,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>21</v>
@@ -4037,7 +4040,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>22</v>
@@ -4069,7 +4072,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -4112,16 +4115,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4146,16 +4149,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>45</v>
@@ -4166,13 +4169,13 @@
         <v>20330051920041</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4183,13 +4186,13 @@
         <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -4200,13 +4203,13 @@
         <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4217,13 +4220,13 @@
         <v>20330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4234,13 +4237,13 @@
         <v>20330051920074</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4251,13 +4254,13 @@
         <v>19330051920014</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4268,13 +4271,13 @@
         <v>19330051920051</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4285,13 +4288,13 @@
         <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4302,13 +4305,13 @@
         <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4319,13 +4322,13 @@
         <v>20330051920081</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4336,13 +4339,13 @@
         <v>20330051920082</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4353,13 +4356,13 @@
         <v>20330051920087</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4370,13 +4373,13 @@
         <v>19330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4387,13 +4390,13 @@
         <v>20330051920091</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4404,13 +4407,13 @@
         <v>20330051920093</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4421,13 +4424,13 @@
         <v>18330051920077</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4438,13 +4441,13 @@
         <v>20330051920061</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4455,13 +4458,13 @@
         <v>20330051920063</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4472,13 +4475,13 @@
         <v>20330051920064</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4489,13 +4492,13 @@
         <v>20330051920065</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4506,13 +4509,13 @@
         <v>20330051920066</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4523,13 +4526,13 @@
         <v>20330051920068</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4540,13 +4543,13 @@
         <v>20330051920070</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4568,16 +4571,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4594,19 +4597,19 @@
         <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4617,13 +4620,13 @@
         <v>18330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4640,13 +4643,13 @@
         <v>20330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4663,13 +4666,13 @@
         <v>20330051920063</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4686,13 +4689,13 @@
         <v>20330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -162,12 +161,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
@@ -189,193 +188,67 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ESPINOZA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
     <t>ALEXIS YAIR</t>
   </si>
   <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -428,11 +301,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,22 +747,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -921,10 +795,10 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -950,22 +824,22 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1027,22 +901,22 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1063,7 +937,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1072,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1104,22 +978,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1140,13 +1014,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1155,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1181,22 +1055,22 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1246,10 +1120,10 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1258,7 +1132,7 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1287,22 +1161,22 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1323,7 +1197,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1364,22 +1238,22 @@
         <v>4</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1441,22 +1315,22 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1518,22 +1392,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1566,10 +1440,10 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1595,22 +1469,22 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1672,22 +1546,22 @@
         <v>4</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1717,10 +1591,10 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1737,10 +1611,10 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1749,7 +1623,7 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1778,22 +1652,22 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1855,22 +1729,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1906,7 +1780,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1923,13 +1797,13 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1941,13 +1815,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1973,22 +1847,22 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2021,10 +1895,10 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2050,22 +1924,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2086,7 +1960,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2095,13 +1969,13 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2127,22 +2001,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2163,7 +2037,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2178,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2204,22 +2078,22 @@
         <v>4</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2246,7 +2120,7 @@
         <v>5</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2281,22 +2155,22 @@
         <v>4</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2358,22 +2232,22 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2400,10 +2274,10 @@
         <v>8</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2435,22 +2309,22 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2622,22 +2496,22 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2681,22 +2555,22 @@
         <v>76</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2740,22 +2614,22 @@
         <v>76</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2799,22 +2673,22 @@
         <v>92</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2905,10 +2779,10 @@
         <v>77.5</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2940,22 +2814,22 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2999,19 +2873,19 @@
         <v>72</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -3058,22 +2932,22 @@
         <v>80</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3117,22 +2991,22 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3176,22 +3050,22 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3235,22 +3109,22 @@
         <v>76</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3282,10 +3156,10 @@
         <v>40</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3317,22 +3191,22 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3376,22 +3250,22 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -3426,13 +3300,13 @@
         <v>88</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -3467,22 +3341,22 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -3526,22 +3400,22 @@
         <v>92</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -3585,22 +3459,22 @@
         <v>92</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -3644,22 +3518,22 @@
         <v>76</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -3703,19 +3577,19 @@
         <v>76</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -3762,22 +3636,22 @@
         <v>92</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -3821,22 +3695,22 @@
         <v>92</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -3873,6 +3747,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3909,65 +3785,65 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>40</v>
-      </c>
-      <c r="G2">
-        <v>60</v>
+        <v>14</v>
+      </c>
+      <c r="F2" s="2">
+        <v>33.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>66.7</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>9</v>
       </c>
       <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>42.86</v>
-      </c>
-      <c r="G3">
-        <v>57.14</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45</v>
+      </c>
+      <c r="G3" s="2">
+        <v>55</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3982,16 +3858,16 @@
         <v>21</v>
       </c>
       <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>47.62</v>
-      </c>
-      <c r="G4">
-        <v>52.38</v>
+      <c r="F4" s="2">
+        <v>52.4</v>
+      </c>
+      <c r="G4" s="2">
+        <v>47.6</v>
       </c>
       <c r="H4">
         <v>5.9</v>
@@ -3999,7 +3875,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4019,11 +3895,11 @@
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5">
-        <v>66.67</v>
-      </c>
-      <c r="G5">
-        <v>33.33</v>
+      <c r="F5" s="2">
+        <v>66.7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>33.3</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -4031,7 +3907,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4046,16 +3922,16 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>77.27</v>
-      </c>
-      <c r="G6">
-        <v>22.73</v>
+        <v>7</v>
+      </c>
+      <c r="F6" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>31.8</v>
       </c>
       <c r="H6">
         <v>6.5</v>
@@ -4063,7 +3939,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4083,19 +3959,19 @@
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7">
-        <v>77.27</v>
-      </c>
-      <c r="G7">
-        <v>22.73</v>
+      <c r="F7" s="2">
+        <v>77.3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>22.7</v>
       </c>
       <c r="H7">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4140,429 +4016,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920041</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920071</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920073</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920359</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920074</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>19330051920014</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>19330051920051</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920077</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920080</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920081</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920082</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920087</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>19330051920067</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920091</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920093</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>18330051920077</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920061</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920063</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920064</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920065</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920066</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>20330051920068</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920070</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4594,22 +4048,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920067</v>
+        <v>20330051920087</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4617,22 +4071,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4643,13 +4097,13 @@
         <v>20330051920061</v>
       </c>
       <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
         <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" t="s">
-        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4663,19 +4117,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920063</v>
+        <v>20330051920061</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>47</v>
@@ -4686,24 +4140,116 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920068</v>
+        <v>20330051920063</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>48</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920063</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920014</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920067</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -170,12 +170,12 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,6 +188,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
@@ -197,15 +200,15 @@
     <t>ROSETE</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -222,6 +225,9 @@
   </si>
   <si>
     <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
@@ -750,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -827,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -904,7 +910,7 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -981,7 +987,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1058,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1164,7 +1170,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -1200,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1241,7 +1247,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1318,7 +1324,7 @@
         <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1395,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1472,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -1549,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1655,7 +1661,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -1691,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1732,7 +1738,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -1800,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -1850,7 +1856,7 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -1927,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2004,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>7</v>
@@ -2081,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2158,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2235,7 +2241,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>7</v>
@@ -2312,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2499,7 +2505,7 @@
         <v>120</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>95</v>
@@ -2558,7 +2564,7 @@
         <v>96</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>90</v>
@@ -2617,7 +2623,7 @@
         <v>104</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>90</v>
@@ -2676,7 +2682,7 @@
         <v>120</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>90</v>
@@ -2817,7 +2823,7 @@
         <v>112</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>90</v>
@@ -2876,7 +2882,7 @@
         <v>60</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>45</v>
@@ -2935,7 +2941,7 @@
         <v>116</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>90</v>
@@ -2994,7 +3000,7 @@
         <v>112</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>95</v>
@@ -3053,7 +3059,7 @@
         <v>116</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>90</v>
@@ -3112,7 +3118,7 @@
         <v>120</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>95</v>
@@ -3194,7 +3200,7 @@
         <v>116</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>80</v>
@@ -3253,7 +3259,7 @@
         <v>120</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>95</v>
@@ -3303,7 +3309,7 @@
         <v>112</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>88</v>
@@ -3344,7 +3350,7 @@
         <v>108</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>80</v>
@@ -3403,7 +3409,7 @@
         <v>116</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>90</v>
@@ -3462,7 +3468,7 @@
         <v>108</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>85</v>
@@ -3521,7 +3527,7 @@
         <v>112</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>85</v>
@@ -3580,7 +3586,7 @@
         <v>68</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>40</v>
@@ -3639,7 +3645,7 @@
         <v>96</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>80</v>
@@ -3698,7 +3704,7 @@
         <v>116</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>75</v>
@@ -3881,28 +3887,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="G5" s="2">
-        <v>33.3</v>
+        <v>31.8</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3913,28 +3919,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>15</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>68.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3948,7 +3954,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7">
         <v>22</v>
@@ -4016,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4048,7 +4054,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -4057,13 +4063,13 @@
         <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4071,7 +4077,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -4080,7 +4086,7 @@
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4094,7 +4100,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -4103,7 +4109,7 @@
         <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4117,7 +4123,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -4126,7 +4132,7 @@
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4140,7 +4146,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920063</v>
+        <v>20330051920061</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -4149,13 +4155,13 @@
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4163,7 +4169,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920063</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -4172,7 +4178,7 @@
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4186,7 +4192,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920014</v>
+        <v>20330051920063</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -4195,13 +4201,13 @@
         <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4209,22 +4215,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920067</v>
+        <v>20330051920063</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4232,24 +4238,70 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920068</v>
+        <v>19330051920014</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>73</v>
       </c>
       <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920067</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920068</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F12" t="s">
         <v>47</v>
       </c>
-      <c r="G10">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -2484,58 +2484,58 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="E4">
-        <v>97.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F4">
         <v>92</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
       </c>
       <c r="J4">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K4">
-        <v>87.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L4">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2543,58 +2543,58 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="E5">
-        <v>70</v>
+        <v>68.3</v>
       </c>
       <c r="F5">
         <v>84</v>
       </c>
       <c r="G5">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H5">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>90</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K5">
-        <v>92.5</v>
+        <v>80.2</v>
       </c>
       <c r="L5">
-        <v>108</v>
+        <v>87.3</v>
       </c>
       <c r="M5">
-        <v>104</v>
+        <v>91.8</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2602,58 +2602,58 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>72</v>
       </c>
       <c r="D6">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E6">
-        <v>82.5</v>
+        <v>80.5</v>
       </c>
       <c r="F6">
         <v>80</v>
       </c>
       <c r="G6">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H6">
-        <v>104</v>
+        <v>93.3</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J6">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K6">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="L6">
-        <v>84</v>
+        <v>74.5</v>
       </c>
       <c r="M6">
-        <v>104</v>
+        <v>91.8</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>74.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2661,58 +2661,58 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="E7">
-        <v>102.5</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
       <c r="G7">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="K7">
-        <v>80</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M7">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2720,58 +2720,58 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C8">
         <v>72</v>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8">
         <v>60</v>
       </c>
       <c r="G8">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2779,22 +2779,22 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="E9">
-        <v>77.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J9">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K9">
-        <v>80</v>
+        <v>77.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2802,58 +2802,58 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>72</v>
       </c>
       <c r="D10">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="E10">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F10">
         <v>80</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>95.2</v>
       </c>
       <c r="K10">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L10">
-        <v>80</v>
+        <v>72.7</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>87.8</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2861,58 +2861,58 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C11">
         <v>72</v>
       </c>
       <c r="D11">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="E11">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F11">
         <v>60</v>
       </c>
       <c r="G11">
-        <v>72</v>
+        <v>78.3</v>
       </c>
       <c r="H11">
         <v>60</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J11">
-        <v>45</v>
+        <v>57.1</v>
       </c>
       <c r="K11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>72.7</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>57.1</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2920,58 +2920,58 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="C12">
         <v>80</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>92.5</v>
+        <v>90.2</v>
       </c>
       <c r="F12">
         <v>76</v>
       </c>
       <c r="G12">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H12">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J12">
+        <v>90.5</v>
+      </c>
+      <c r="K12">
+        <v>82.7</v>
+      </c>
+      <c r="L12">
+        <v>78.2</v>
+      </c>
+      <c r="M12">
+        <v>91.8</v>
+      </c>
+      <c r="N12">
+        <v>96.7</v>
+      </c>
+      <c r="O12">
         <v>90</v>
       </c>
-      <c r="K12">
-        <v>75</v>
-      </c>
-      <c r="L12">
-        <v>96</v>
-      </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>82.7</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>78.2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2979,58 +2979,58 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>105</v>
+        <v>91.3</v>
       </c>
       <c r="E13">
-        <v>97.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F13">
         <v>100</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="I13">
         <v>100</v>
       </c>
       <c r="J13">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="K13">
-        <v>77.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3038,58 +3038,58 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>72</v>
       </c>
       <c r="D14">
-        <v>105</v>
+        <v>91.3</v>
       </c>
       <c r="E14">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F14">
         <v>72</v>
       </c>
       <c r="G14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J14">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L14">
-        <v>88</v>
+        <v>72.7</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>87.8</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3097,58 +3097,58 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E15">
-        <v>92.5</v>
+        <v>90.2</v>
       </c>
       <c r="F15">
         <v>96</v>
       </c>
       <c r="G15">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H15">
-        <v>120</v>
+        <v>98.3</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K15">
-        <v>82.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L15">
-        <v>108</v>
+        <v>92.7</v>
       </c>
       <c r="M15">
-        <v>104</v>
+        <v>91.8</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3156,22 +3156,22 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J16">
-        <v>90</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3179,58 +3179,58 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E17">
-        <v>97.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F17">
         <v>72</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H17">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="K17">
-        <v>80</v>
+        <v>87.7</v>
       </c>
       <c r="L17">
-        <v>108</v>
+        <v>81.8</v>
       </c>
       <c r="M17">
-        <v>92</v>
+        <v>87.8</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3238,58 +3238,58 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="E18">
-        <v>97.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F18">
         <v>92</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K18">
-        <v>82.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L18">
-        <v>120</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3297,31 +3297,31 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="G19">
-        <v>88</v>
+        <v>95.7</v>
       </c>
       <c r="H19">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3329,58 +3329,58 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F20">
         <v>92</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>108</v>
+        <v>93.3</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>80</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K20">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="L20">
-        <v>104</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M20">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3388,58 +3388,58 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
       </c>
       <c r="D21">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="E21">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="F21">
         <v>88</v>
       </c>
       <c r="G21">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H21">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>90</v>
+        <v>85.7</v>
       </c>
       <c r="K21">
-        <v>82.5</v>
+        <v>87.7</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="M21">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3447,58 +3447,58 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22">
-        <v>105</v>
+        <v>91.3</v>
       </c>
       <c r="E22">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F22">
         <v>76</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H22">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>85</v>
+        <v>90.5</v>
       </c>
       <c r="K22">
-        <v>75</v>
+        <v>80.2</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M22">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3506,58 +3506,58 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>72</v>
       </c>
       <c r="D23">
-        <v>105</v>
+        <v>91.3</v>
       </c>
       <c r="E23">
-        <v>92.5</v>
+        <v>90.2</v>
       </c>
       <c r="F23">
         <v>88</v>
       </c>
       <c r="G23">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H23">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="J23">
-        <v>85</v>
+        <v>90.5</v>
       </c>
       <c r="K23">
-        <v>77.5</v>
+        <v>84</v>
       </c>
       <c r="L23">
-        <v>92</v>
+        <v>81.8</v>
       </c>
       <c r="M23">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="N23">
+        <v>96.7</v>
+      </c>
+      <c r="O23">
+        <v>86</v>
+      </c>
+      <c r="P23">
+        <v>90.5</v>
+      </c>
+      <c r="Q23">
         <v>84</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
       <c r="R23">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3565,58 +3565,58 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>92</v>
+        <v>76.7</v>
       </c>
       <c r="C24">
         <v>68</v>
       </c>
       <c r="D24">
-        <v>65</v>
+        <v>56.5</v>
       </c>
       <c r="E24">
-        <v>32.5</v>
+        <v>31.7</v>
       </c>
       <c r="F24">
         <v>60</v>
       </c>
       <c r="G24">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H24">
-        <v>68</v>
+        <v>66.7</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="J24">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K24">
-        <v>15</v>
+        <v>23.5</v>
       </c>
       <c r="L24">
-        <v>80</v>
+        <v>63.6</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3624,58 +3624,58 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>104</v>
+        <v>86.7</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E25">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F25">
         <v>96</v>
       </c>
       <c r="G25">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>96</v>
+        <v>83.3</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="K25">
-        <v>77.5</v>
+        <v>81.5</v>
       </c>
       <c r="L25">
-        <v>92</v>
+        <v>85.5</v>
       </c>
       <c r="M25">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>81.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>85.5</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3683,58 +3683,58 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>110</v>
+        <v>95.7</v>
       </c>
       <c r="E26">
-        <v>92.5</v>
+        <v>90.2</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H26">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>75</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K26">
-        <v>82.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L26">
-        <v>112</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M26">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -2508,10 +2508,10 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>94.5</v>
@@ -2526,10 +2526,10 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R4">
         <v>94.5</v>
@@ -2567,10 +2567,10 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K5">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="L5">
         <v>87.3</v>
@@ -2585,10 +2585,10 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="Q5">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="R5">
         <v>87.3</v>
@@ -2626,10 +2626,10 @@
         <v>86</v>
       </c>
       <c r="J6">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="K6">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="L6">
         <v>74.5</v>
@@ -2644,10 +2644,10 @@
         <v>86</v>
       </c>
       <c r="P6">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q6">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="R6">
         <v>74.5</v>
@@ -2685,10 +2685,10 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K7">
-        <v>90.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L7">
         <v>90.90000000000001</v>
@@ -2703,10 +2703,10 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q7">
-        <v>90.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R7">
         <v>90.90000000000001</v>
@@ -2744,10 +2744,10 @@
         <v>36</v>
       </c>
       <c r="J8">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="K8">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="L8">
         <v>27.3</v>
@@ -2762,10 +2762,10 @@
         <v>36</v>
       </c>
       <c r="P8">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="Q8">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="R8">
         <v>27.3</v>
@@ -2785,16 +2785,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="J9">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K9">
-        <v>77.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="P9">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="Q9">
-        <v>77.8</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2826,10 +2826,10 @@
         <v>86</v>
       </c>
       <c r="J10">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K10">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L10">
         <v>72.7</v>
@@ -2844,10 +2844,10 @@
         <v>86</v>
       </c>
       <c r="P10">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q10">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R10">
         <v>72.7</v>
@@ -2885,10 +2885,10 @@
         <v>86</v>
       </c>
       <c r="J11">
-        <v>57.1</v>
+        <v>58.5</v>
       </c>
       <c r="K11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L11">
         <v>72.7</v>
@@ -2903,10 +2903,10 @@
         <v>86</v>
       </c>
       <c r="P11">
-        <v>57.1</v>
+        <v>58.5</v>
       </c>
       <c r="Q11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R11">
         <v>72.7</v>
@@ -2944,10 +2944,10 @@
         <v>90</v>
       </c>
       <c r="J12">
+        <v>92.7</v>
+      </c>
+      <c r="K12">
         <v>90.5</v>
-      </c>
-      <c r="K12">
-        <v>82.7</v>
       </c>
       <c r="L12">
         <v>78.2</v>
@@ -2962,10 +2962,10 @@
         <v>90</v>
       </c>
       <c r="P12">
+        <v>92.7</v>
+      </c>
+      <c r="Q12">
         <v>90.5</v>
-      </c>
-      <c r="Q12">
-        <v>82.7</v>
       </c>
       <c r="R12">
         <v>78.2</v>
@@ -3003,10 +3003,10 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K13">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3021,10 +3021,10 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3062,10 +3062,10 @@
         <v>86</v>
       </c>
       <c r="J14">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K14">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L14">
         <v>72.7</v>
@@ -3080,10 +3080,10 @@
         <v>86</v>
       </c>
       <c r="P14">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q14">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R14">
         <v>72.7</v>
@@ -3121,10 +3121,10 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K15">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L15">
         <v>92.7</v>
@@ -3139,10 +3139,10 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q15">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R15">
         <v>92.7</v>
@@ -3162,16 +3162,16 @@
         <v>39</v>
       </c>
       <c r="J16">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K16">
-        <v>69.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="P16">
-        <v>78.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="Q16">
-        <v>69.09999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3203,10 +3203,10 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="K17">
-        <v>87.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L17">
         <v>81.8</v>
@@ -3221,10 +3221,10 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="Q17">
-        <v>87.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R17">
         <v>81.8</v>
@@ -3262,10 +3262,10 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>88.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="L18">
         <v>96.40000000000001</v>
@@ -3280,10 +3280,10 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>88.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="R18">
         <v>96.40000000000001</v>
@@ -3353,10 +3353,10 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K20">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L20">
         <v>89.09999999999999</v>
@@ -3371,10 +3371,10 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>92.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q20">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R20">
         <v>89.09999999999999</v>
@@ -3412,10 +3412,10 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="K21">
-        <v>87.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L21">
         <v>85.5</v>
@@ -3430,10 +3430,10 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="Q21">
-        <v>87.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R21">
         <v>85.5</v>
@@ -3471,10 +3471,10 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>90.5</v>
+        <v>92.7</v>
       </c>
       <c r="K22">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="L22">
         <v>80</v>
@@ -3489,10 +3489,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>90.5</v>
+        <v>92.7</v>
       </c>
       <c r="Q22">
-        <v>80.2</v>
+        <v>87.8</v>
       </c>
       <c r="R22">
         <v>80</v>
@@ -3530,10 +3530,10 @@
         <v>86</v>
       </c>
       <c r="J23">
-        <v>90.5</v>
+        <v>92.7</v>
       </c>
       <c r="K23">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L23">
         <v>81.8</v>
@@ -3548,10 +3548,10 @@
         <v>86</v>
       </c>
       <c r="P23">
-        <v>90.5</v>
+        <v>92.7</v>
       </c>
       <c r="Q23">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="R23">
         <v>81.8</v>
@@ -3589,10 +3589,10 @@
         <v>84</v>
       </c>
       <c r="J24">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="K24">
-        <v>23.5</v>
+        <v>25.7</v>
       </c>
       <c r="L24">
         <v>63.6</v>
@@ -3607,10 +3607,10 @@
         <v>84</v>
       </c>
       <c r="P24">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="Q24">
-        <v>23.5</v>
+        <v>25.7</v>
       </c>
       <c r="R24">
         <v>63.6</v>
@@ -3648,10 +3648,10 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="K25">
-        <v>81.5</v>
+        <v>89.2</v>
       </c>
       <c r="L25">
         <v>85.5</v>
@@ -3666,10 +3666,10 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>85.7</v>
+        <v>87.8</v>
       </c>
       <c r="Q25">
-        <v>81.5</v>
+        <v>89.2</v>
       </c>
       <c r="R25">
         <v>85.5</v>
@@ -3707,10 +3707,10 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="K26">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L26">
         <v>96.40000000000001</v>
@@ -3725,10 +3725,10 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>88.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q26">
-        <v>86.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R26">
         <v>96.40000000000001</v>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="72">
   <si>
     <t>Materia</t>
   </si>
@@ -161,21 +161,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,64 +188,52 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
     <t>MONTERO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -771,10 +759,10 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -783,10 +771,10 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -848,10 +836,10 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -860,13 +848,13 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -881,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -925,10 +913,10 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -937,16 +925,16 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -958,7 +946,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1002,10 +990,10 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1014,16 +1002,16 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>6</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1079,10 +1067,10 @@
         <v>4</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1091,10 +1079,10 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1185,10 +1173,10 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1197,16 +1185,16 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1215,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1262,10 +1250,10 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1274,10 +1262,10 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1339,10 +1327,10 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1351,16 +1339,16 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>5</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1369,10 +1357,10 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1416,10 +1404,10 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1428,16 +1416,16 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1449,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1493,10 +1481,10 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1505,16 +1493,16 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1526,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1570,10 +1558,10 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1582,16 +1570,16 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>5</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1603,7 +1591,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1676,10 +1664,10 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1688,16 +1676,16 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1706,10 +1694,10 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1753,10 +1741,10 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1765,16 +1753,16 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -1812,13 +1800,13 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -1871,10 +1859,10 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -1883,16 +1871,16 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -1904,7 +1892,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -1948,10 +1936,10 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -1960,13 +1948,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2025,10 +2013,10 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2037,16 +2025,16 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2055,10 +2043,10 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2102,10 +2090,10 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2114,16 +2102,16 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2132,10 +2120,10 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2179,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2191,10 +2179,10 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2256,10 +2244,10 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2268,13 +2256,13 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2289,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2333,10 +2321,10 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2345,10 +2333,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2366,7 +2354,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2508,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -2532,7 +2520,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>94.5</v>
+        <v>96.2</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2579,7 +2567,7 @@
         <v>91.8</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>56.7</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2591,10 +2579,10 @@
         <v>87.8</v>
       </c>
       <c r="R5">
-        <v>87.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="S5">
-        <v>91.8</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2638,10 +2626,10 @@
         <v>91.8</v>
       </c>
       <c r="N6">
-        <v>93.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="P6">
         <v>90.2</v>
@@ -2650,10 +2638,10 @@
         <v>87.8</v>
       </c>
       <c r="R6">
-        <v>74.5</v>
+        <v>77.2</v>
       </c>
       <c r="S6">
-        <v>91.8</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2697,7 +2685,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2709,7 +2697,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="R7">
-        <v>90.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2756,10 +2744,10 @@
         <v>38.8</v>
       </c>
       <c r="N8">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="O8">
-        <v>36</v>
+        <v>22.5</v>
       </c>
       <c r="P8">
         <v>24.4</v>
@@ -2768,10 +2756,10 @@
         <v>21.6</v>
       </c>
       <c r="R8">
-        <v>27.3</v>
+        <v>19</v>
       </c>
       <c r="S8">
-        <v>38.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2838,10 +2826,10 @@
         <v>87.8</v>
       </c>
       <c r="N10">
-        <v>96.7</v>
+        <v>90</v>
       </c>
       <c r="O10">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="P10">
         <v>97.59999999999999</v>
@@ -2850,10 +2838,10 @@
         <v>94.59999999999999</v>
       </c>
       <c r="R10">
-        <v>72.7</v>
+        <v>81</v>
       </c>
       <c r="S10">
-        <v>87.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2897,10 +2885,10 @@
         <v>36.7</v>
       </c>
       <c r="N11">
-        <v>60</v>
+        <v>45.6</v>
       </c>
       <c r="O11">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P11">
         <v>58.5</v>
@@ -2909,10 +2897,10 @@
         <v>23</v>
       </c>
       <c r="R11">
-        <v>72.7</v>
+        <v>50.6</v>
       </c>
       <c r="S11">
-        <v>36.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2956,10 +2944,10 @@
         <v>91.8</v>
       </c>
       <c r="N12">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O12">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P12">
         <v>92.7</v>
@@ -2968,10 +2956,10 @@
         <v>90.5</v>
       </c>
       <c r="R12">
-        <v>78.2</v>
+        <v>83.5</v>
       </c>
       <c r="S12">
-        <v>91.8</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3074,10 +3062,10 @@
         <v>87.8</v>
       </c>
       <c r="N14">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="P14">
         <v>95.09999999999999</v>
@@ -3086,10 +3074,10 @@
         <v>91.90000000000001</v>
       </c>
       <c r="R14">
-        <v>72.7</v>
+        <v>81</v>
       </c>
       <c r="S14">
-        <v>87.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3133,7 +3121,7 @@
         <v>91.8</v>
       </c>
       <c r="N15">
-        <v>98.3</v>
+        <v>93.3</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3145,10 +3133,10 @@
         <v>94.59999999999999</v>
       </c>
       <c r="R15">
-        <v>92.7</v>
+        <v>93.7</v>
       </c>
       <c r="S15">
-        <v>91.8</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3215,7 +3203,7 @@
         <v>87.8</v>
       </c>
       <c r="N17">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3227,10 +3215,10 @@
         <v>95.90000000000001</v>
       </c>
       <c r="R17">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
       <c r="S17">
-        <v>87.8</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3286,7 +3274,7 @@
         <v>97.3</v>
       </c>
       <c r="R18">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3315,13 +3303,13 @@
         <v>89.8</v>
       </c>
       <c r="N19">
-        <v>93.3</v>
+        <v>92.2</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3365,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3377,7 +3365,7 @@
         <v>91.90000000000001</v>
       </c>
       <c r="R20">
-        <v>89.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3424,7 +3412,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>98.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3436,7 +3424,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="R21">
-        <v>85.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3483,7 +3471,7 @@
         <v>89.8</v>
       </c>
       <c r="N22">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -3495,10 +3483,10 @@
         <v>87.8</v>
       </c>
       <c r="R22">
-        <v>80</v>
+        <v>84.8</v>
       </c>
       <c r="S22">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3542,10 +3530,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N23">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O23">
-        <v>86</v>
+        <v>91.3</v>
       </c>
       <c r="P23">
         <v>92.7</v>
@@ -3554,10 +3542,10 @@
         <v>91.90000000000001</v>
       </c>
       <c r="R23">
-        <v>81.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="S23">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3601,10 +3589,10 @@
         <v>38.8</v>
       </c>
       <c r="N24">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="O24">
-        <v>84</v>
+        <v>52.5</v>
       </c>
       <c r="P24">
         <v>51.2</v>
@@ -3613,10 +3601,10 @@
         <v>25.7</v>
       </c>
       <c r="R24">
-        <v>63.6</v>
+        <v>44.3</v>
       </c>
       <c r="S24">
-        <v>38.8</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3660,7 +3648,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -3672,7 +3660,7 @@
         <v>89.2</v>
       </c>
       <c r="R25">
-        <v>85.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -3719,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>98.3</v>
+        <v>96.7</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -3731,7 +3719,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="R26">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -3791,7 +3779,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
@@ -3800,19 +3788,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>33.3</v>
+        <v>61.9</v>
       </c>
       <c r="G2" s="2">
-        <v>66.7</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3823,28 +3811,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>45</v>
+        <v>68.2</v>
       </c>
       <c r="G3" s="2">
-        <v>55</v>
+        <v>31.8</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3855,28 +3843,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>52.4</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2">
-        <v>47.6</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3887,28 +3875,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>22</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>68.2</v>
+        <v>77.3</v>
       </c>
       <c r="G5" s="2">
-        <v>31.8</v>
+        <v>22.7</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3922,25 +3910,25 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>21</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G6" s="2">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3951,28 +3939,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>77.3</v>
+        <v>85.7</v>
       </c>
       <c r="G7" s="2">
-        <v>22.7</v>
+        <v>14.3</v>
       </c>
       <c r="H7">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4022,7 +4010,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4054,22 +4042,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920065</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4077,22 +4065,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920051</v>
+        <v>20330051920065</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4100,22 +4088,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>19330051920014</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4123,19 +4111,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>20330051920080</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>47</v>
@@ -4146,7 +4134,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920061</v>
+        <v>20330051920082</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -4155,10 +4143,10 @@
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>49</v>
@@ -4169,19 +4157,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
@@ -4192,116 +4180,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920063</v>
+        <v>19330051920067</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>48</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920063</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920014</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920067</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920068</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -164,12 +164,12 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -188,52 +188,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
   </si>
   <si>
     <t>URBINA</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
   </si>
   <si>
     <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
   </si>
 </sst>
 </file>
@@ -765,10 +777,10 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -842,10 +854,10 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>4</v>
@@ -860,10 +872,10 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -919,10 +931,10 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -937,10 +949,10 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -996,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1073,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>4</v>
@@ -1120,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1179,10 +1191,10 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1200,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1256,10 +1268,10 @@
         <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>4</v>
@@ -1333,10 +1345,10 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>7</v>
@@ -1351,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1410,10 +1422,10 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1487,10 +1499,10 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1505,7 +1517,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1564,10 +1576,10 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1611,10 +1623,10 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1670,10 +1682,10 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -1747,10 +1759,10 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>8</v>
@@ -1865,10 +1877,10 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>8</v>
@@ -1942,10 +1954,10 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -1960,10 +1972,10 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2019,10 +2031,10 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2040,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2096,10 +2108,10 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>7</v>
@@ -2114,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2173,10 +2185,10 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>4</v>
@@ -2250,10 +2262,10 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>7</v>
@@ -2327,10 +2339,10 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>7</v>
@@ -2514,7 +2526,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2573,10 +2585,10 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>80.5</v>
+        <v>88.3</v>
       </c>
       <c r="Q5">
-        <v>87.8</v>
+        <v>91.2</v>
       </c>
       <c r="R5">
         <v>86.09999999999999</v>
@@ -2632,10 +2644,10 @@
         <v>91.3</v>
       </c>
       <c r="P6">
-        <v>90.2</v>
+        <v>93.3</v>
       </c>
       <c r="Q6">
-        <v>87.8</v>
+        <v>91.2</v>
       </c>
       <c r="R6">
         <v>77.2</v>
@@ -2691,10 +2703,10 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>97.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="Q7">
-        <v>98.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R7">
         <v>88.59999999999999</v>
@@ -2750,10 +2762,10 @@
         <v>22.5</v>
       </c>
       <c r="P8">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="Q8">
-        <v>21.6</v>
+        <v>14</v>
       </c>
       <c r="R8">
         <v>19</v>
@@ -2779,10 +2791,10 @@
         <v>85.09999999999999</v>
       </c>
       <c r="P9">
-        <v>80.5</v>
+        <v>86.7</v>
       </c>
       <c r="Q9">
-        <v>85.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2832,10 +2844,10 @@
         <v>91.3</v>
       </c>
       <c r="P10">
-        <v>97.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="Q10">
-        <v>94.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R10">
         <v>81</v>
@@ -2891,10 +2903,10 @@
         <v>85</v>
       </c>
       <c r="P11">
-        <v>58.5</v>
+        <v>40</v>
       </c>
       <c r="Q11">
-        <v>23</v>
+        <v>14.9</v>
       </c>
       <c r="R11">
         <v>50.6</v>
@@ -2950,10 +2962,10 @@
         <v>93.8</v>
       </c>
       <c r="P12">
-        <v>92.7</v>
+        <v>93.3</v>
       </c>
       <c r="Q12">
-        <v>90.5</v>
+        <v>93</v>
       </c>
       <c r="R12">
         <v>83.5</v>
@@ -3009,10 +3021,10 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>97.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="Q13">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3068,10 +3080,10 @@
         <v>91.3</v>
       </c>
       <c r="P14">
-        <v>95.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Q14">
-        <v>91.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R14">
         <v>81</v>
@@ -3127,10 +3139,10 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="Q15">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="R15">
         <v>93.7</v>
@@ -3156,10 +3168,10 @@
         <v>75.7</v>
       </c>
       <c r="P16">
-        <v>80.5</v>
+        <v>88.3</v>
       </c>
       <c r="Q16">
-        <v>75.7</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3209,10 +3221,10 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>87.8</v>
+        <v>90</v>
       </c>
       <c r="Q17">
-        <v>95.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R17">
         <v>87.3</v>
@@ -3271,7 +3283,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>97.3</v>
+        <v>96.5</v>
       </c>
       <c r="R18">
         <v>97.5</v>
@@ -3359,10 +3371,10 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="Q20">
-        <v>91.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R20">
         <v>92.40000000000001</v>
@@ -3418,10 +3430,10 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>87.8</v>
+        <v>90</v>
       </c>
       <c r="Q21">
-        <v>95.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="R21">
         <v>89.90000000000001</v>
@@ -3477,10 +3489,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="Q22">
-        <v>87.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R22">
         <v>84.8</v>
@@ -3536,10 +3548,10 @@
         <v>91.3</v>
       </c>
       <c r="P23">
-        <v>92.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q23">
-        <v>91.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="R23">
         <v>86.09999999999999</v>
@@ -3595,10 +3607,10 @@
         <v>52.5</v>
       </c>
       <c r="P24">
-        <v>51.2</v>
+        <v>35</v>
       </c>
       <c r="Q24">
-        <v>25.7</v>
+        <v>16.7</v>
       </c>
       <c r="R24">
         <v>44.3</v>
@@ -3654,10 +3666,10 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>87.8</v>
+        <v>90</v>
       </c>
       <c r="Q25">
-        <v>89.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R25">
         <v>88.59999999999999</v>
@@ -3713,10 +3725,10 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>90.2</v>
+        <v>91.7</v>
       </c>
       <c r="Q26">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="R26">
         <v>96.2</v>
@@ -3811,28 +3823,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>68.2</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2">
-        <v>31.8</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3843,28 +3855,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="G4" s="2">
-        <v>30</v>
+        <v>18.2</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3875,28 +3887,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>77.3</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>22.7</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3907,10 +3919,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>21</v>
@@ -3928,7 +3940,7 @@
         <v>14.3</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3939,28 +3951,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>85.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4010,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4042,16 +4054,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920065</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4065,19 +4077,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920065</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>48</v>
@@ -4088,22 +4100,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920014</v>
+        <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4111,22 +4123,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920080</v>
+        <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4134,7 +4146,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920082</v>
+        <v>20330051920080</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -4143,13 +4155,13 @@
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4157,22 +4169,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
         <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4180,24 +4192,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920067</v>
+        <v>20330051920087</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
         <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920067</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920065</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20222.xlsx
+++ b/grupos/6AEV - Estadisticos 20222.xlsx
@@ -2212,7 +2212,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -3598,7 +3598,7 @@
         <v>63.6</v>
       </c>
       <c r="M24">
-        <v>38.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N24">
         <v>44.4</v>
@@ -3616,7 +3616,7 @@
         <v>44.3</v>
       </c>
       <c r="S24">
-        <v>60.5</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3919,28 +3919,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3951,28 +3951,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
         <v>19</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>86.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="G7" s="2">
-        <v>13.6</v>
+        <v>9.5</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I7">
         <v>0</v>
